--- a/_stats_outputs/approach1_coefs.xlsx
+++ b/_stats_outputs/approach1_coefs.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,35 +362,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>transect</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>slope_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>array_est</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>forest_est</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>forest_err</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>forest_pval</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>bsfs_pval</t>
         </is>
@@ -402,30 +407,33 @@
           <t>ASH</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>-0.1129983344345611</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E2">
-        <v>-0.1099500281330161</v>
+        <v>-3.43966962604106</v>
       </c>
       <c r="F2">
-        <v>0.02208115430345806</v>
+        <v>-3.346878856369181</v>
       </c>
       <c r="G2">
-        <v>0.00760330289113405</v>
+        <v>0.6721129136707557</v>
       </c>
       <c r="H2">
-        <v>0.2363607743115644</v>
+        <v>0.007599082179277888</v>
+      </c>
+      <c r="I2">
+        <v>0.2363310793492502</v>
       </c>
     </row>
     <row r="3">
@@ -434,27 +442,30 @@
           <t>ASH</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>-0.0719062010005207</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E3">
-        <v>-0.06648442193803078</v>
+        <v>-2.188825338024531</v>
       </c>
       <c r="F3">
-        <v>0.02208115430345806</v>
+        <v>-2.023785803793768</v>
       </c>
       <c r="G3">
-        <v>0.03952130285439882</v>
+        <v>0.6721129136707557</v>
+      </c>
+      <c r="H3">
+        <v>0.03950779448759779</v>
       </c>
     </row>
     <row r="4">
@@ -463,30 +474,33 @@
           <t>ASH</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>north</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.0832101707015612</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E4">
-        <v>-0.1099500281330161</v>
+        <v>-2.53291473776113</v>
       </c>
       <c r="F4">
-        <v>0.02208115430345806</v>
+        <v>-3.346878856369181</v>
       </c>
       <c r="G4">
-        <v>0.00760330289113405</v>
+        <v>0.6721129136707557</v>
       </c>
       <c r="H4">
-        <v>0.2363607743115644</v>
+        <v>0.007599082179277888</v>
+      </c>
+      <c r="I4">
+        <v>0.2363310793492502</v>
       </c>
     </row>
     <row r="5">
@@ -495,27 +509,30 @@
           <t>ASH</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>north</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.08806313633592451</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E5">
-        <v>-0.06648442193803078</v>
+        <v>-2.680644176752418</v>
       </c>
       <c r="F5">
-        <v>0.02208115430345806</v>
+        <v>-2.023785803793768</v>
       </c>
       <c r="G5">
-        <v>0.03952130285439882</v>
+        <v>0.6721129136707557</v>
+      </c>
+      <c r="H5">
+        <v>0.03950779448759779</v>
       </c>
     </row>
     <row r="6">
@@ -524,30 +541,33 @@
           <t>ASH</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>south</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-0.1336415792629273</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E6">
-        <v>-0.1099500281330161</v>
+        <v>-4.068052205305038</v>
       </c>
       <c r="F6">
-        <v>0.02208115430345806</v>
+        <v>-3.346878856369181</v>
       </c>
       <c r="G6">
-        <v>0.00760330289113405</v>
+        <v>0.6721129136707557</v>
       </c>
       <c r="H6">
-        <v>0.2363607743115644</v>
+        <v>0.007599082179277888</v>
+      </c>
+      <c r="I6">
+        <v>0.2363310793492502</v>
       </c>
     </row>
     <row r="7">
@@ -556,27 +576,30 @@
           <t>ASH</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>south</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.03948392847764764</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E7">
-        <v>-0.06648442193803078</v>
+        <v>-1.201887896604137</v>
       </c>
       <c r="F7">
-        <v>0.02208115430345806</v>
+        <v>-2.023785803793768</v>
       </c>
       <c r="G7">
-        <v>0.03952130285439882</v>
+        <v>0.6721129136707557</v>
+      </c>
+      <c r="H7">
+        <v>0.03950779448759779</v>
       </c>
     </row>
     <row r="8">
@@ -585,30 +608,33 @@
           <t>LRE</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.08650991621987611</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E8">
-        <v>-0.08713038623871192</v>
+        <v>-2.633364456883923</v>
       </c>
       <c r="F8">
-        <v>0.02115574599446191</v>
+        <v>-2.652248957106386</v>
       </c>
       <c r="G8">
-        <v>0.01462883216168791</v>
+        <v>0.6439708931541994</v>
       </c>
       <c r="H8">
-        <v>0.7201775909078458</v>
+        <v>0.01462924584275813</v>
+      </c>
+      <c r="I8">
+        <v>0.7201742245241556</v>
       </c>
     </row>
     <row r="9">
@@ -617,27 +643,30 @@
           <t>LRE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>-0.07448112169915312</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E9">
-        <v>-0.07562675860489435</v>
+        <v>-2.267210158370099</v>
       </c>
       <c r="F9">
-        <v>0.02115574599446191</v>
+        <v>-2.302078531932976</v>
       </c>
       <c r="G9">
-        <v>0.02327477328922685</v>
+        <v>0.6439708931541994</v>
+      </c>
+      <c r="H9">
+        <v>0.02327515101231295</v>
       </c>
     </row>
     <row r="10">
@@ -646,30 +675,33 @@
           <t>LRE</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>east</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>-0.07958440696949878</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E10">
-        <v>-0.08713038623871192</v>
+        <v>-2.422581055576597</v>
       </c>
       <c r="F10">
-        <v>0.02115574599446191</v>
+        <v>-2.652248957106386</v>
       </c>
       <c r="G10">
-        <v>0.01462883216168791</v>
+        <v>0.6439708931541994</v>
       </c>
       <c r="H10">
-        <v>0.7201775909078458</v>
+        <v>0.01462924584275813</v>
+      </c>
+      <c r="I10">
+        <v>0.7201742245241556</v>
       </c>
     </row>
     <row r="11">
@@ -678,27 +710,30 @@
           <t>LRE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>east</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>-0.07593433150690154</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E11">
-        <v>-0.07562675860489435</v>
+        <v>-2.311439758680529</v>
       </c>
       <c r="F11">
-        <v>0.02115574599446191</v>
+        <v>-2.302078531932976</v>
       </c>
       <c r="G11">
-        <v>0.02327477328922685</v>
+        <v>0.6439708931541994</v>
+      </c>
+      <c r="H11">
+        <v>0.02327515101231295</v>
       </c>
     </row>
     <row r="12">
@@ -707,30 +742,33 @@
           <t>LRE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>west</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>-0.09529683552676095</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E12">
-        <v>-0.08713038623871192</v>
+        <v>-2.900801358858646</v>
       </c>
       <c r="F12">
-        <v>0.02115574599446191</v>
+        <v>-2.652248957106386</v>
       </c>
       <c r="G12">
-        <v>0.01462883216168791</v>
+        <v>0.6439708931541994</v>
       </c>
       <c r="H12">
-        <v>0.7201775909078458</v>
+        <v>0.01462924584275813</v>
+      </c>
+      <c r="I12">
+        <v>0.7201742245241556</v>
       </c>
     </row>
     <row r="13">
@@ -739,27 +777,30 @@
           <t>LRE</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>west</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>-0.07646482260862839</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E13">
-        <v>-0.07562675860489435</v>
+        <v>-2.327585678748309</v>
       </c>
       <c r="F13">
-        <v>0.02115574599446191</v>
+        <v>-2.302078531932976</v>
       </c>
       <c r="G13">
-        <v>0.02327477328922685</v>
+        <v>0.6439708931541994</v>
+      </c>
+      <c r="H13">
+        <v>0.02327515101231295</v>
       </c>
     </row>
     <row r="14">
@@ -768,30 +809,33 @@
           <t>LRJ</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14">
+        <v>2.266754270696452</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>-0.09920023029332374</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E14">
-        <v>-0.08509700829383855</v>
+        <v>-3.021961950374457</v>
       </c>
       <c r="F14">
-        <v>0.02158017125684102</v>
+        <v>-2.590352932464441</v>
       </c>
       <c r="G14">
-        <v>0.01688135327572915</v>
+        <v>0.6575253010120951</v>
       </c>
       <c r="H14">
-        <v>0.5619367150353907</v>
+        <v>0.01696578943374394</v>
+      </c>
+      <c r="I14">
+        <v>0.5623225497890948</v>
       </c>
     </row>
     <row r="15">
@@ -800,27 +844,30 @@
           <t>LRJ</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15">
+        <v>2.266754270696452</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>-0.07607682796475231</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E15">
-        <v>-0.06582247235387013</v>
+        <v>-2.317456003615712</v>
       </c>
       <c r="F15">
-        <v>0.02158017125684102</v>
+        <v>-2.0036360584518</v>
       </c>
       <c r="G15">
-        <v>0.03797497833378304</v>
+        <v>0.6575253010120951</v>
+      </c>
+      <c r="H15">
+        <v>0.03813044306717106</v>
       </c>
     </row>
     <row r="16">
@@ -829,30 +876,33 @@
           <t>LRJ</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16">
+        <v>2.266754270696452</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>north</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>-0.0869232851142737</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E16">
-        <v>-0.08509700829383855</v>
+        <v>-2.646243532848426</v>
       </c>
       <c r="F16">
-        <v>0.02158017125684102</v>
+        <v>-2.590352932464441</v>
       </c>
       <c r="G16">
-        <v>0.01688135327572915</v>
+        <v>0.6575253010120951</v>
       </c>
       <c r="H16">
-        <v>0.5619367150353907</v>
+        <v>0.01696578943374394</v>
+      </c>
+      <c r="I16">
+        <v>0.5623225497890948</v>
       </c>
     </row>
     <row r="17">
@@ -861,27 +911,30 @@
           <t>LRJ</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17">
+        <v>2.266754270696452</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>north</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>-0.0585051487145938</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E17">
-        <v>-0.06582247235387013</v>
+        <v>-1.779699792696849</v>
       </c>
       <c r="F17">
-        <v>0.02158017125684102</v>
+        <v>-2.0036360584518</v>
       </c>
       <c r="G17">
-        <v>0.03797497833378304</v>
+        <v>0.6575253010120951</v>
+      </c>
+      <c r="H17">
+        <v>0.03813044306717106</v>
       </c>
     </row>
     <row r="18">
@@ -890,30 +943,33 @@
           <t>LRJ</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18">
+        <v>2.266754270696452</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>south</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>-0.06916750947391852</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E18">
-        <v>-0.08509700829383855</v>
+        <v>-2.10285331417045</v>
       </c>
       <c r="F18">
-        <v>0.02158017125684102</v>
+        <v>-2.590352932464441</v>
       </c>
       <c r="G18">
-        <v>0.01688135327572915</v>
+        <v>0.6575253010120951</v>
       </c>
       <c r="H18">
-        <v>0.5619367150353907</v>
+        <v>0.01696578943374394</v>
+      </c>
+      <c r="I18">
+        <v>0.5623225497890948</v>
       </c>
     </row>
     <row r="19">
@@ -922,27 +978,30 @@
           <t>LRJ</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19">
+        <v>2.266754270696452</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>south</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>-0.0628854403822646</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E19">
-        <v>-0.06582247235387013</v>
+        <v>-1.913752379042851</v>
       </c>
       <c r="F19">
-        <v>0.02158017125684102</v>
+        <v>-2.0036360584518</v>
       </c>
       <c r="G19">
-        <v>0.03797497833378304</v>
+        <v>0.6575253010120951</v>
+      </c>
+      <c r="H19">
+        <v>0.03813044306717106</v>
       </c>
     </row>
     <row r="20">
@@ -951,30 +1010,33 @@
           <t>LRW</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>-0.07585813784190525</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E20">
-        <v>-0.07585813784190525</v>
+        <v>-2.309121715907596</v>
       </c>
       <c r="F20">
-        <v>0.01888584974157758</v>
+        <v>-2.309121715907596</v>
       </c>
       <c r="G20">
-        <v>0.0003087090181520174</v>
+        <v>0.574885038347449</v>
       </c>
       <c r="H20">
-        <v>0.249089876411302</v>
+        <v>0.0003087071503610556</v>
+      </c>
+      <c r="I20">
+        <v>0.2490888123193706</v>
       </c>
     </row>
     <row r="21">
@@ -983,27 +1045,30 @@
           <t>LRW</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>-0.1071778685708674</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E21">
-        <v>-0.1071778685708674</v>
+        <v>-3.262494319297206</v>
       </c>
       <c r="F21">
-        <v>0.01888584974157758</v>
+        <v>-3.262494319297206</v>
       </c>
       <c r="G21">
-        <v>2.277280928703217E-06</v>
+        <v>0.574885038347449</v>
+      </c>
+      <c r="H21">
+        <v>2.277256934190319E-06</v>
       </c>
     </row>
     <row r="22">
@@ -1012,30 +1077,33 @@
           <t>LRW</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>north</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>-0.07585813784190525</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E22">
-        <v>-0.07585813784190525</v>
+        <v>-2.309121715907596</v>
       </c>
       <c r="F22">
-        <v>0.01888584974157758</v>
+        <v>-2.309121715907596</v>
       </c>
       <c r="G22">
-        <v>0.0003087090181520174</v>
+        <v>0.574885038347449</v>
       </c>
       <c r="H22">
-        <v>0.249089876411302</v>
+        <v>0.0003087071503610556</v>
+      </c>
+      <c r="I22">
+        <v>0.2490888123193706</v>
       </c>
     </row>
     <row r="23">
@@ -1044,27 +1112,30 @@
           <t>LRW</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>north</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>-0.1071778685708674</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E23">
-        <v>-0.1071778685708674</v>
+        <v>-3.262494319297206</v>
       </c>
       <c r="F23">
-        <v>0.01888584974157758</v>
+        <v>-3.262494319297206</v>
       </c>
       <c r="G23">
-        <v>2.277280928703217E-06</v>
+        <v>0.574885038347449</v>
+      </c>
+      <c r="H23">
+        <v>2.277256934190319E-06</v>
       </c>
     </row>
     <row r="24">
@@ -1073,30 +1144,33 @@
           <t>LRW</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>south</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>-0.07585813784190525</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E24">
-        <v>-0.07585813784190525</v>
+        <v>-2.309121715907596</v>
       </c>
       <c r="F24">
-        <v>0.01888584974157758</v>
+        <v>-2.309121715907596</v>
       </c>
       <c r="G24">
-        <v>0.0003087090181520174</v>
+        <v>0.574885038347449</v>
       </c>
       <c r="H24">
-        <v>0.249089876411302</v>
+        <v>0.0003087071503610556</v>
+      </c>
+      <c r="I24">
+        <v>0.2490888123193706</v>
       </c>
     </row>
     <row r="25">
@@ -1105,27 +1179,30 @@
           <t>LRW</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25">
+        <v>2.529566360052562</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>south</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>-0.1071778685708674</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E25">
-        <v>-0.1071778685708674</v>
+        <v>-3.262494319297206</v>
       </c>
       <c r="F25">
-        <v>0.01888584974157758</v>
+        <v>-3.262494319297206</v>
       </c>
       <c r="G25">
-        <v>2.277280928703217E-06</v>
+        <v>0.574885038347449</v>
+      </c>
+      <c r="H25">
+        <v>2.277256934190319E-06</v>
       </c>
     </row>
     <row r="26">
@@ -1134,30 +1211,33 @@
           <t>MAG</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26">
+        <v>2.299605781865966</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>0.05807906039020726</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E26">
-        <v>-0.105438475666129</v>
+        <v>1.206850786230586</v>
       </c>
       <c r="F26">
-        <v>2.252500192242869</v>
+        <v>-3.209547199264947</v>
       </c>
       <c r="G26">
-        <v>0.9627158501779811</v>
+        <v>3.051674051339206</v>
       </c>
       <c r="H26">
-        <v>0.993040134545105</v>
+        <v>0.3522607045418362</v>
+      </c>
+      <c r="I26">
+        <v>0.8539754684526759</v>
       </c>
     </row>
     <row r="27">
@@ -1166,27 +1246,30 @@
           <t>MAG</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27">
+        <v>2.299605781865966</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>0.09532213085892333</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E27">
-        <v>-0.07761336942380861</v>
+        <v>2.308214100622732</v>
       </c>
       <c r="F27">
-        <v>2.252500192242869</v>
+        <v>-2.362550965254707</v>
       </c>
       <c r="G27">
-        <v>0.9725504831174745</v>
+        <v>3.051674051339206</v>
+      </c>
+      <c r="H27">
+        <v>0.4820366224397812</v>
       </c>
     </row>
     <row r="28">
@@ -1195,30 +1278,33 @@
           <t>MAG</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28">
+        <v>2.299605781865966</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>east</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>-0.2882303443800104</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E28">
-        <v>-0.105438475666129</v>
+        <v>-8.14652007829919</v>
       </c>
       <c r="F28">
-        <v>2.252500192242869</v>
+        <v>-3.209547199264947</v>
       </c>
       <c r="G28">
-        <v>0.9627158501779811</v>
+        <v>3.051674051339206</v>
       </c>
       <c r="H28">
-        <v>0.993040134545105</v>
+        <v>0.3522607045418362</v>
+      </c>
+      <c r="I28">
+        <v>0.8539754684526759</v>
       </c>
     </row>
     <row r="29">
@@ -1227,27 +1313,30 @@
           <t>MAG</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29">
+        <v>2.299605781865966</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>east</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>-0.2511723019964042</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E29">
-        <v>-0.07761336942380861</v>
+        <v>-7.050154134110005</v>
       </c>
       <c r="F29">
-        <v>2.252500192242869</v>
+        <v>-2.362550965254707</v>
       </c>
       <c r="G29">
-        <v>0.9725504831174745</v>
+        <v>3.051674051339206</v>
+      </c>
+      <c r="H29">
+        <v>0.4820366224397812</v>
       </c>
     </row>
     <row r="30">
@@ -1256,30 +1345,33 @@
           <t>MAG</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30">
+        <v>2.299605781865966</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>west</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>-0.08616414300744314</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E30">
-        <v>-0.105438475666129</v>
+        <v>-2.688972305727372</v>
       </c>
       <c r="F30">
-        <v>2.252500192242869</v>
+        <v>-3.209547199264947</v>
       </c>
       <c r="G30">
-        <v>0.9627158501779811</v>
+        <v>3.051674051339206</v>
       </c>
       <c r="H30">
-        <v>0.993040134545105</v>
+        <v>0.3522607045418362</v>
+      </c>
+      <c r="I30">
+        <v>0.8539754684526759</v>
       </c>
     </row>
     <row r="31">
@@ -1288,27 +1380,30 @@
           <t>MAG</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31">
+        <v>2.299605781865966</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>west</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>-0.07698993713338859</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E31">
-        <v>-0.07761336942380861</v>
+        <v>-2.345712862277858</v>
       </c>
       <c r="F31">
-        <v>2.252500192242869</v>
+        <v>-2.362550965254707</v>
       </c>
       <c r="G31">
-        <v>0.9725504831174745</v>
+        <v>3.051674051339206</v>
+      </c>
+      <c r="H31">
+        <v>0.4820366224397812</v>
       </c>
     </row>
     <row r="32">
@@ -1317,30 +1412,33 @@
           <t>WD</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>-0.06620368768976483</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E32">
-        <v>-0.06620368768976483</v>
+        <v>-2.015240253276509</v>
       </c>
       <c r="F32">
-        <v>0.02906836393202467</v>
+        <v>-2.015240253276509</v>
       </c>
       <c r="G32">
-        <v>0.02916395425573451</v>
+        <v>0.8848316662159894</v>
       </c>
       <c r="H32">
-        <v>0.8166356787510268</v>
+        <v>0.02916216361765942</v>
+      </c>
+      <c r="I32">
+        <v>0.8166337376052223</v>
       </c>
     </row>
     <row r="33">
@@ -1349,27 +1447,30 @@
           <t>WD</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>-0.0565974143894846</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E33">
-        <v>-0.0565974143894846</v>
+        <v>-1.722825294015962</v>
       </c>
       <c r="F33">
-        <v>0.02906836393202467</v>
+        <v>-1.722825294015962</v>
       </c>
       <c r="G33">
-        <v>0.05982827465344489</v>
+        <v>0.8848316662159894</v>
+      </c>
+      <c r="H33">
+        <v>0.05982545801930361</v>
       </c>
     </row>
     <row r="34">
@@ -1378,30 +1479,33 @@
           <t>WD</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>east</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>-0.06620368768976483</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E34">
-        <v>-0.06620368768976483</v>
+        <v>-2.015240253276509</v>
       </c>
       <c r="F34">
-        <v>0.02906836393202467</v>
+        <v>-2.015240253276509</v>
       </c>
       <c r="G34">
-        <v>0.02916395425573451</v>
+        <v>0.8848316662159894</v>
       </c>
       <c r="H34">
-        <v>0.8166356787510268</v>
+        <v>0.02916216361765942</v>
+      </c>
+      <c r="I34">
+        <v>0.8166337376052223</v>
       </c>
     </row>
     <row r="35">
@@ -1410,27 +1514,30 @@
           <t>WD</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>east</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>-0.0565974143894846</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E35">
-        <v>-0.0565974143894846</v>
+        <v>-1.722825294015962</v>
       </c>
       <c r="F35">
-        <v>0.02906836393202467</v>
+        <v>-1.722825294015962</v>
       </c>
       <c r="G35">
-        <v>0.05982827465344489</v>
+        <v>0.8848316662159894</v>
+      </c>
+      <c r="H35">
+        <v>0.05982545801930361</v>
       </c>
     </row>
     <row r="36">
@@ -1439,30 +1546,33 @@
           <t>WD</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>west</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>-0.06620368768976483</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
       </c>
       <c r="E36">
-        <v>-0.06620368768976483</v>
+        <v>-2.015240253276509</v>
       </c>
       <c r="F36">
-        <v>0.02906836393202467</v>
+        <v>-2.015240253276509</v>
       </c>
       <c r="G36">
-        <v>0.02916395425573451</v>
+        <v>0.8848316662159894</v>
       </c>
       <c r="H36">
-        <v>0.8166356787510268</v>
+        <v>0.02916216361765942</v>
+      </c>
+      <c r="I36">
+        <v>0.8166337376052223</v>
       </c>
     </row>
     <row r="37">
@@ -1471,27 +1581,30 @@
           <t>WD</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37">
+        <v>2.398160315374507</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>west</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>-0.0565974143894846</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
       </c>
       <c r="E37">
-        <v>-0.0565974143894846</v>
+        <v>-1.722825294015962</v>
       </c>
       <c r="F37">
-        <v>0.02906836393202467</v>
+        <v>-1.722825294015962</v>
       </c>
       <c r="G37">
-        <v>0.05982827465344489</v>
+        <v>0.8848316662159894</v>
+      </c>
+      <c r="H37">
+        <v>0.05982545801930361</v>
       </c>
     </row>
   </sheetData>
